--- a/exports/trend_1d/ANANDRATHI_full_report.xlsx
+++ b/exports/trend_1d/ANANDRATHI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>11.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44613</v>
+        <v>44614</v>
       </c>
       <c r="H2" t="n">
-        <v>140.8</v>
+        <v>140.1</v>
       </c>
       <c r="I2" t="n">
         <v>140.639788277</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.54</v>
+        <v>-2.03</v>
       </c>
       <c r="L2" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="M2" t="n">
         <v>2.84</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.02</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44649</v>
+        <v>44650</v>
       </c>
       <c r="H3" t="n">
-        <v>148.8</v>
+        <v>151.6</v>
       </c>
       <c r="I3" t="n">
         <v>151.4988654573066</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.21</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>7.35</v>
+        <v>11.21</v>
       </c>
       <c r="M3" t="n">
         <v>2.27</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.22</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H4" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I4" t="n">
         <v>154.8923390061794</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>2.24</v>
+        <v>0.92</v>
       </c>
       <c r="L4" t="n">
         <v>0.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.73</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44781</v>
+        <v>44783</v>
       </c>
       <c r="H5" t="n">
-        <v>168.1</v>
+        <v>169.6</v>
       </c>
       <c r="I5" t="n">
         <v>169.5297243038098</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.869999999999999</v>
+        <v>-10.85</v>
       </c>
       <c r="L5" t="n">
         <v>13.2</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44911</v>
+        <v>44914</v>
       </c>
       <c r="H6" t="n">
-        <v>170.2</v>
+        <v>169.6</v>
       </c>
       <c r="I6" t="n">
         <v>170.1059935691785</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K6" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>5.72</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.26</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44929</v>
+        <v>44930</v>
       </c>
       <c r="H7" t="n">
-        <v>176.1</v>
+        <v>179</v>
       </c>
       <c r="I7" t="n">
         <v>177.2331044628832</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.83</v>
+        <v>-5.54</v>
       </c>
       <c r="L7" t="n">
-        <v>4.19</v>
+        <v>5.84</v>
       </c>
       <c r="M7" t="n">
         <v>0.74</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H8" t="n">
-        <v>199.6</v>
+        <v>190.7</v>
       </c>
       <c r="I8" t="n">
         <v>194.307059391631</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>11.51</v>
+        <v>6.54</v>
       </c>
       <c r="L8" t="n">
         <v>1.62</v>
@@ -897,7 +992,7 @@
         <v>0.32</v>
       </c>
       <c r="N8" t="n">
-        <v>4.08</v>
+        <v>4.46</v>
       </c>
       <c r="O8" t="n">
         <v>1.65</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>14.17</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45012</v>
+        <v>45013</v>
       </c>
       <c r="H9" t="n">
-        <v>202.9</v>
+        <v>204.1</v>
       </c>
       <c r="I9" t="n">
         <v>203.5453522913284</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.4</v>
+        <v>-7.03</v>
       </c>
       <c r="L9" t="n">
         <v>8.550000000000001</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.57</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H10" t="n">
-        <v>943</v>
+        <v>894</v>
       </c>
       <c r="I10" t="n">
         <v>901.4395123242593</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>362.03</v>
+        <v>338.02</v>
       </c>
       <c r="L10" t="n">
         <v>2.6</v>
@@ -1011,7 +1130,7 @@
         <v>3.31</v>
       </c>
       <c r="N10" t="n">
-        <v>4.53</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
         <v>0.59</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>240</v>
+        <v>241</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>13</v>
+      </c>
+      <c r="U10" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>14.71</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45390</v>
+        <v>45391</v>
       </c>
       <c r="H11" t="n">
-        <v>934.4</v>
+        <v>1018</v>
       </c>
       <c r="I11" t="n">
         <v>990.9925142464514</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.52</v>
+        <v>-13.87</v>
       </c>
       <c r="L11" t="n">
-        <v>7.83</v>
+        <v>14.63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.62</v>
+        <v>6.43</v>
       </c>
       <c r="N11" t="n">
-        <v>2.94</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-5.2</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>15.3</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H12" t="n">
-        <v>1023.2</v>
+        <v>958.5</v>
       </c>
       <c r="I12" t="n">
         <v>971.0921264189294</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K12" t="n">
-        <v>0.51</v>
+        <v>-5.84</v>
       </c>
       <c r="L12" t="n">
-        <v>5.68</v>
+        <v>13.04</v>
       </c>
       <c r="M12" t="n">
         <v>3.21</v>
       </c>
       <c r="N12" t="n">
-        <v>4.05</v>
+        <v>6.32</v>
       </c>
       <c r="O12" t="n">
         <v>8.949999999999999</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.22</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H13" t="n">
-        <v>960.3</v>
+        <v>982.2</v>
       </c>
       <c r="I13" t="n">
         <v>974.4229531856713</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.19</v>
+        <v>-2.47</v>
       </c>
       <c r="L13" t="n">
         <v>12.01</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.37</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45646</v>
+        <v>45649</v>
       </c>
       <c r="H14" t="n">
-        <v>1015.6</v>
+        <v>982.1</v>
       </c>
       <c r="I14" t="n">
         <v>996.5384618854113</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
         <v>4.4</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>12.44</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45708</v>
+        <v>45709</v>
       </c>
       <c r="H15" t="n">
-        <v>965.4</v>
+        <v>1001.6</v>
       </c>
       <c r="I15" t="n">
         <v>984.4532531721566</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7</v>
+        <v>-1.99</v>
       </c>
       <c r="L15" t="n">
         <v>8.19</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H16" t="n">
-        <v>932.5</v>
+        <v>899.5</v>
       </c>
       <c r="I16" t="n">
         <v>913.2016465474524</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.9</v>
+        <v>-10.19</v>
       </c>
       <c r="L16" t="n">
-        <v>9.49</v>
+        <v>12.09</v>
       </c>
       <c r="M16" t="n">
         <v>1.51</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.11</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="H17" t="n">
-        <v>922</v>
+        <v>941.6</v>
       </c>
       <c r="I17" t="n">
         <v>932.6578981216846</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.5</v>
+        <v>-4.68</v>
       </c>
       <c r="L17" t="n">
         <v>8.56</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="H18" t="n">
-        <v>1433.4</v>
+        <v>1405.9</v>
       </c>
       <c r="I18" t="n">
         <v>1427.226977566112</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K18" t="n">
-        <v>52.23</v>
+        <v>49.31</v>
       </c>
       <c r="L18" t="n">
         <v>2.7</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="H19" t="n">
-        <v>1467.4</v>
+        <v>1581.6</v>
       </c>
       <c r="I19" t="n">
         <v>1523.404480593759</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.37</v>
+        <v>-12.5</v>
       </c>
       <c r="L19" t="n">
-        <v>7.76</v>
+        <v>18.12</v>
       </c>
       <c r="M19" t="n">
-        <v>0.47</v>
+        <v>3.79</v>
       </c>
       <c r="N19" t="n">
-        <v>2.62</v>
+        <v>7.78</v>
       </c>
       <c r="O19" t="n">
         <v>-1.92</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.34</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="H20" t="n">
-        <v>1470.8</v>
+        <v>1435.2</v>
       </c>
       <c r="I20" t="n">
         <v>1437.511696008418</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.01</v>
+        <v>-9.26</v>
       </c>
       <c r="L20" t="n">
-        <v>7.81</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>1.22</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="H21" t="n">
-        <v>1515.2</v>
+        <v>1531.2</v>
       </c>
       <c r="I21" t="n">
         <v>1526.710690416788</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.57</v>
+        <v>-6.69</v>
       </c>
       <c r="L21" t="n">
-        <v>6.26</v>
+        <v>7.48</v>
       </c>
       <c r="M21" t="n">
         <v>1.19</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>6.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="H22" t="n">
-        <v>1504.2</v>
+        <v>1479.7</v>
       </c>
       <c r="I22" t="n">
         <v>1489.557148778093</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.76</v>
+        <v>-3.36</v>
       </c>
       <c r="L22" t="n">
-        <v>2.53</v>
+        <v>4.1</v>
       </c>
       <c r="M22" t="n">
         <v>0.87</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.27</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H23" t="n">
-        <v>1538</v>
+        <v>1574.2</v>
       </c>
       <c r="I23" t="n">
         <v>1562.691064809812</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.94</v>
+        <v>-6.39</v>
       </c>
       <c r="L23" t="n">
-        <v>4.65</v>
+        <v>7.43</v>
       </c>
       <c r="M23" t="n">
         <v>2.74</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.76</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="H24" t="n">
-        <v>1501.7</v>
+        <v>1456.2</v>
       </c>
       <c r="I24" t="n">
         <v>1493.584110745819</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.61</v>
+        <v>-7.5</v>
       </c>
       <c r="L24" t="n">
         <v>7.79</v>
@@ -1809,7 +2096,7 @@
         <v>2.38</v>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
         <v>2.35</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.44</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H25" t="n">
-        <v>1557.3</v>
+        <v>1604.1</v>
       </c>
       <c r="I25" t="n">
         <v>1593.691631835363</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.94</v>
+        <v>-10.16</v>
       </c>
       <c r="L25" t="n">
-        <v>8.5</v>
+        <v>10.7</v>
       </c>
       <c r="M25" t="n">
         <v>0.65</v>
       </c>
       <c r="N25" t="n">
-        <v>2.61</v>
+        <v>3.01</v>
       </c>
       <c r="O25" t="n">
         <v>-3.03</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.23</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="H26" t="n">
-        <v>2146.2</v>
+        <v>2100.6</v>
       </c>
       <c r="I26" t="n">
         <v>2113.683626161998</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K26" t="n">
-        <v>33.79</v>
+        <v>30.95</v>
       </c>
       <c r="L26" t="n">
         <v>4.85</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H27" t="n">
-        <v>2230</v>
+        <v>2259</v>
       </c>
       <c r="I27" t="n">
         <v>2238.548080352063</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.16</v>
+        <v>-7.54</v>
       </c>
       <c r="L27" t="n">
-        <v>6.73</v>
+        <v>7.94</v>
       </c>
       <c r="M27" t="n">
         <v>0.55</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2040,6 +2375,12 @@
       <c r="Q28" t="n">
         <v>2</v>
       </c>
+      <c r="R28" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4176,7 +4517,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.3</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="6">
@@ -4186,7 +4527,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="7">
@@ -4196,7 +4537,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8">
@@ -4206,7 +4547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -4216,7 +4557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -4226,7 +4567,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -4266,7 +4607,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.82</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="15">
@@ -4276,7 +4617,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.17</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="16">
@@ -4286,7 +4627,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-4.52</v>
+        <v>-7.53</v>
       </c>
     </row>
     <row r="17">
@@ -4296,7 +4637,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>362.03</v>
+        <v>338.02</v>
       </c>
     </row>
     <row r="18">
@@ -4306,7 +4647,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="19">
@@ -4316,7 +4657,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -4326,7 +4667,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.5</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="21">
@@ -4336,7 +4677,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.2</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="22">
@@ -4346,7 +4687,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -4356,7 +4697,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -4366,7 +4707,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="25">
@@ -4376,7 +4717,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.06</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="26">
@@ -4386,7 +4727,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.59</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="27">
@@ -4396,7 +4737,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.28</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -4406,7 +4747,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
